--- a/AAII_Financials/Yearly/NHI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NHI_YR_FIN.xlsx
@@ -792,7 +792,7 @@
         <v>51100</v>
       </c>
       <c r="G9" s="3">
-        <v>9800</v>
+        <v>38000</v>
       </c>
       <c r="H9" s="3">
         <v>11600</v>
@@ -843,7 +843,7 @@
         <v>269300</v>
       </c>
       <c r="G10" s="3">
-        <v>269000</v>
+        <v>240800</v>
       </c>
       <c r="H10" s="3">
         <v>285500</v>
